--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.2362</v>
+        <v>16.65727</v>
       </c>
       <c r="D2" t="n">
-        <v>16.90502</v>
+        <v>16.56763</v>
       </c>
       <c r="E2" t="n">
-        <v>16.83751</v>
+        <v>16.65288</v>
       </c>
       <c r="F2" t="n">
-        <v>42.94866</v>
+        <v>42.13036</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05067</v>
+        <v>0.05167</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81408</v>
+        <v>1.7946</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.69981</v>
+        <v>17.12644</v>
       </c>
       <c r="D3" t="n">
-        <v>16.26757</v>
+        <v>16.69552</v>
       </c>
       <c r="E3" t="n">
-        <v>16.66239</v>
+        <v>16.9041</v>
       </c>
       <c r="F3" t="n">
-        <v>42.34291</v>
+        <v>42.58785</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05048</v>
+        <v>0.05137</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84688</v>
+        <v>1.83331</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.57984</v>
+        <v>16.9463</v>
       </c>
       <c r="D4" t="n">
-        <v>16.59712</v>
+        <v>16.75202</v>
       </c>
       <c r="E4" t="n">
-        <v>16.73437</v>
+        <v>16.85602</v>
       </c>
       <c r="F4" t="n">
-        <v>42.74148</v>
+        <v>41.5418</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05127</v>
+        <v>0.0514</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82158</v>
+        <v>1.8292</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.23255</v>
+        <v>16.91295</v>
       </c>
       <c r="D5" t="n">
-        <v>16.51292</v>
+        <v>16.56258</v>
       </c>
       <c r="E5" t="n">
-        <v>17.02358</v>
+        <v>16.90475</v>
       </c>
       <c r="F5" t="n">
-        <v>43.82946</v>
+        <v>42.73489</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05078</v>
+        <v>0.05026</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81769</v>
+        <v>1.79027</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.95833</v>
+        <v>17.01541</v>
       </c>
       <c r="D6" t="n">
-        <v>16.79251</v>
+        <v>16.53551</v>
       </c>
       <c r="E6" t="n">
-        <v>16.68411</v>
+        <v>17.00369</v>
       </c>
       <c r="F6" t="n">
-        <v>41.70205</v>
+        <v>41.93886</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04975</v>
+        <v>0.05056</v>
       </c>
       <c r="H6" t="n">
-        <v>1.84288</v>
+        <v>1.84276</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.96289</v>
+        <v>17.13776</v>
       </c>
       <c r="D7" t="n">
-        <v>16.84904</v>
+        <v>16.52389</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75911</v>
+        <v>16.76541</v>
       </c>
       <c r="F7" t="n">
-        <v>42.84452</v>
+        <v>43.0731</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04983</v>
+        <v>0.05095</v>
       </c>
       <c r="H7" t="n">
-        <v>1.86509</v>
+        <v>1.82628</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.08129</v>
+        <v>16.92252</v>
       </c>
       <c r="D8" t="n">
-        <v>16.55075</v>
+        <v>16.52515</v>
       </c>
       <c r="E8" t="n">
-        <v>16.54591</v>
+        <v>16.66631</v>
       </c>
       <c r="F8" t="n">
-        <v>42.37371</v>
+        <v>42.93278</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05236</v>
+        <v>0.0517</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83861</v>
+        <v>1.84712</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.71512</v>
+        <v>16.92561</v>
       </c>
       <c r="D9" t="n">
-        <v>16.48564</v>
+        <v>16.54953</v>
       </c>
       <c r="E9" t="n">
-        <v>16.5705</v>
+        <v>16.70022</v>
       </c>
       <c r="F9" t="n">
-        <v>42.00818</v>
+        <v>42.8151</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05091</v>
+        <v>0.05125</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80222</v>
+        <v>1.78924</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.87676</v>
+        <v>17.24912</v>
       </c>
       <c r="D10" t="n">
-        <v>16.59269</v>
+        <v>16.83259</v>
       </c>
       <c r="E10" t="n">
-        <v>16.56721</v>
+        <v>16.88234</v>
       </c>
       <c r="F10" t="n">
-        <v>42.59424</v>
+        <v>42.90518</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05027</v>
+        <v>0.05092</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85812</v>
+        <v>1.86983</v>
       </c>
     </row>
     <row r="11">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.11691</v>
+        <v>17.18282</v>
       </c>
       <c r="D12" t="n">
-        <v>16.832</v>
+        <v>16.34129</v>
       </c>
       <c r="E12" t="n">
-        <v>16.37613</v>
+        <v>16.81004</v>
       </c>
       <c r="F12" t="n">
-        <v>43.10551</v>
+        <v>43.71093</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05135</v>
+        <v>0.05018</v>
       </c>
       <c r="H12" t="n">
-        <v>1.83933</v>
+        <v>1.80659</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.65578</v>
+        <v>17.17544</v>
       </c>
       <c r="D13" t="n">
-        <v>16.62031</v>
+        <v>16.40605</v>
       </c>
       <c r="E13" t="n">
-        <v>16.61966</v>
+        <v>17.10452</v>
       </c>
       <c r="F13" t="n">
-        <v>42.3179</v>
+        <v>42.77973</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05159</v>
+        <v>0.05302</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83671</v>
+        <v>1.80407</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.99472</v>
+        <v>17.13338</v>
       </c>
       <c r="D14" t="n">
-        <v>16.53834</v>
+        <v>16.8184</v>
       </c>
       <c r="E14" t="n">
-        <v>17.08507</v>
+        <v>17.05457</v>
       </c>
       <c r="F14" t="n">
-        <v>42.00126</v>
+        <v>43.07505</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05062</v>
+        <v>0.05085</v>
       </c>
       <c r="H14" t="n">
-        <v>1.87066</v>
+        <v>1.8631</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.44531</v>
+        <v>17.12553</v>
       </c>
       <c r="D15" t="n">
-        <v>16.53696</v>
+        <v>16.67948</v>
       </c>
       <c r="E15" t="n">
-        <v>16.80895</v>
+        <v>16.91794</v>
       </c>
       <c r="F15" t="n">
-        <v>42.56234</v>
+        <v>42.95086</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05031</v>
+        <v>0.05122</v>
       </c>
       <c r="H15" t="n">
-        <v>1.82578</v>
+        <v>1.82061</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.02365</v>
+        <v>16.94418</v>
       </c>
       <c r="D16" t="n">
-        <v>16.522</v>
+        <v>16.66253</v>
       </c>
       <c r="E16" t="n">
-        <v>16.89525</v>
+        <v>16.74243</v>
       </c>
       <c r="F16" t="n">
-        <v>42.55767</v>
+        <v>42.74651</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04972</v>
+        <v>0.05041</v>
       </c>
       <c r="H16" t="n">
-        <v>1.81357</v>
+        <v>1.86617</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.50278</v>
+        <v>17.06114</v>
       </c>
       <c r="D17" t="n">
-        <v>16.57088</v>
+        <v>16.60411</v>
       </c>
       <c r="E17" t="n">
-        <v>16.86855</v>
+        <v>16.93274</v>
       </c>
       <c r="F17" t="n">
-        <v>42.66751</v>
+        <v>43.2179</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0517</v>
+        <v>0.05173</v>
       </c>
       <c r="H17" t="n">
-        <v>1.82873</v>
+        <v>1.79582</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.92453</v>
+        <v>16.80402</v>
       </c>
       <c r="D18" t="n">
-        <v>16.86694</v>
+        <v>16.70625</v>
       </c>
       <c r="E18" t="n">
-        <v>16.8217</v>
+        <v>16.74735</v>
       </c>
       <c r="F18" t="n">
-        <v>42.10691</v>
+        <v>42.35168</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05036</v>
+        <v>0.05076</v>
       </c>
       <c r="H18" t="n">
-        <v>1.82877</v>
+        <v>1.82789</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.63173</v>
+        <v>16.87737</v>
       </c>
       <c r="D19" t="n">
-        <v>16.82161</v>
+        <v>16.55221</v>
       </c>
       <c r="E19" t="n">
-        <v>17.02562</v>
+        <v>16.71862</v>
       </c>
       <c r="F19" t="n">
-        <v>42.18646</v>
+        <v>42.4089</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05053</v>
+        <v>0.05067</v>
       </c>
       <c r="H19" t="n">
-        <v>1.83417</v>
+        <v>1.7951</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.02064</v>
+        <v>16.89523</v>
       </c>
       <c r="D20" t="n">
-        <v>16.61367</v>
+        <v>16.35253</v>
       </c>
       <c r="E20" t="n">
-        <v>16.5425</v>
+        <v>16.56347</v>
       </c>
       <c r="F20" t="n">
-        <v>42.80113</v>
+        <v>43.08122</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05082</v>
+        <v>0.05096</v>
       </c>
       <c r="H20" t="n">
-        <v>1.83385</v>
+        <v>1.78366</v>
       </c>
     </row>
     <row r="21">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.87354</v>
+        <v>16.00828</v>
       </c>
       <c r="D22" t="n">
-        <v>15.73484</v>
+        <v>15.57369</v>
       </c>
       <c r="E22" t="n">
-        <v>15.70948</v>
+        <v>15.82765</v>
       </c>
       <c r="F22" t="n">
-        <v>256.76514</v>
+        <v>255.60119</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.64461</v>
+        <v>15.91121</v>
       </c>
       <c r="D23" t="n">
-        <v>15.34893</v>
+        <v>15.69209</v>
       </c>
       <c r="E23" t="n">
-        <v>15.48306</v>
+        <v>15.75389</v>
       </c>
       <c r="F23" t="n">
-        <v>259.29358</v>
+        <v>255.28997</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.85938</v>
+        <v>15.78824</v>
       </c>
       <c r="D24" t="n">
-        <v>15.61079</v>
+        <v>15.71015</v>
       </c>
       <c r="E24" t="n">
-        <v>15.62688</v>
+        <v>15.74113</v>
       </c>
       <c r="F24" t="n">
-        <v>250.75743</v>
+        <v>261.68718</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.59496</v>
+        <v>15.90991</v>
       </c>
       <c r="D25" t="n">
-        <v>15.8974</v>
+        <v>15.49515</v>
       </c>
       <c r="E25" t="n">
-        <v>15.3558</v>
+        <v>15.64688</v>
       </c>
       <c r="F25" t="n">
-        <v>254.61291</v>
+        <v>256.69977</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.17664</v>
+        <v>16.15021</v>
       </c>
       <c r="D26" t="n">
-        <v>15.80272</v>
+        <v>15.54256</v>
       </c>
       <c r="E26" t="n">
-        <v>15.52849</v>
+        <v>16.11243</v>
       </c>
       <c r="F26" t="n">
-        <v>257.22935</v>
+        <v>256.33165</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.15066</v>
+        <v>15.81664</v>
       </c>
       <c r="D27" t="n">
-        <v>15.70223</v>
+        <v>15.60297</v>
       </c>
       <c r="E27" t="n">
-        <v>15.57507</v>
+        <v>15.67092</v>
       </c>
       <c r="F27" t="n">
-        <v>251.66737</v>
+        <v>255.05339</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.71816</v>
+        <v>15.74166</v>
       </c>
       <c r="D28" t="n">
-        <v>15.57972</v>
+        <v>15.63829</v>
       </c>
       <c r="E28" t="n">
-        <v>15.43481</v>
+        <v>15.67148</v>
       </c>
       <c r="F28" t="n">
-        <v>251.67716</v>
+        <v>259.93719</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.90605</v>
+        <v>15.65129</v>
       </c>
       <c r="D29" t="n">
-        <v>15.79939</v>
+        <v>15.4274</v>
       </c>
       <c r="E29" t="n">
-        <v>15.81246</v>
+        <v>15.64453</v>
       </c>
       <c r="F29" t="n">
-        <v>259.48061</v>
+        <v>253.62684</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.7138</v>
+        <v>15.905</v>
       </c>
       <c r="D30" t="n">
-        <v>15.84943</v>
+        <v>15.36376</v>
       </c>
       <c r="E30" t="n">
-        <v>15.57475</v>
+        <v>15.54644</v>
       </c>
       <c r="F30" t="n">
-        <v>260.3697</v>
+        <v>256.44489</v>
       </c>
     </row>
     <row r="31">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.81314</v>
+        <v>16.91633</v>
       </c>
       <c r="D32" t="n">
-        <v>16.35254</v>
+        <v>15.98031</v>
       </c>
       <c r="E32" t="n">
-        <v>16.45732</v>
+        <v>16.14284</v>
       </c>
       <c r="F32" t="n">
-        <v>21.66362</v>
+        <v>22.22803</v>
       </c>
       <c r="G32" t="n">
-        <v>34.84503</v>
+        <v>34.73598</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.57776</v>
+        <v>16.83177</v>
       </c>
       <c r="D33" t="n">
-        <v>16.27984</v>
+        <v>16.09182</v>
       </c>
       <c r="E33" t="n">
-        <v>16.69415</v>
+        <v>16.47276</v>
       </c>
       <c r="F33" t="n">
-        <v>21.62933</v>
+        <v>22.34941</v>
       </c>
       <c r="G33" t="n">
-        <v>33.52312</v>
+        <v>35.10453</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.79012</v>
+        <v>16.7909</v>
       </c>
       <c r="D34" t="n">
-        <v>16.18873</v>
+        <v>16.04403</v>
       </c>
       <c r="E34" t="n">
-        <v>16.50344</v>
+        <v>16.36322</v>
       </c>
       <c r="F34" t="n">
-        <v>21.85781</v>
+        <v>22.1372</v>
       </c>
       <c r="G34" t="n">
-        <v>34.41487</v>
+        <v>34.50231</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.9768</v>
+        <v>16.48701</v>
       </c>
       <c r="D35" t="n">
-        <v>15.86546</v>
+        <v>16.06973</v>
       </c>
       <c r="E35" t="n">
-        <v>16.64767</v>
+        <v>16.48612</v>
       </c>
       <c r="F35" t="n">
-        <v>22.27016</v>
+        <v>21.85052</v>
       </c>
       <c r="G35" t="n">
-        <v>33.86004</v>
+        <v>34.37983</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.78991</v>
+        <v>16.81917</v>
       </c>
       <c r="D36" t="n">
-        <v>16.37547</v>
+        <v>16.05858</v>
       </c>
       <c r="E36" t="n">
-        <v>16.91349</v>
+        <v>16.46873</v>
       </c>
       <c r="F36" t="n">
-        <v>21.88529</v>
+        <v>21.94138</v>
       </c>
       <c r="G36" t="n">
-        <v>34.57187</v>
+        <v>34.55954</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.43036</v>
+        <v>17.10543</v>
       </c>
       <c r="D37" t="n">
-        <v>16.18706</v>
+        <v>16.12119</v>
       </c>
       <c r="E37" t="n">
-        <v>16.34615</v>
+        <v>16.54685</v>
       </c>
       <c r="F37" t="n">
-        <v>22.20257</v>
+        <v>21.88227</v>
       </c>
       <c r="G37" t="n">
-        <v>33.94786</v>
+        <v>34.73525</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16.93779</v>
+        <v>16.92527</v>
       </c>
       <c r="D38" t="n">
-        <v>16.29548</v>
+        <v>16.03034</v>
       </c>
       <c r="E38" t="n">
-        <v>16.12474</v>
+        <v>16.39373</v>
       </c>
       <c r="F38" t="n">
-        <v>21.77304</v>
+        <v>21.97032</v>
       </c>
       <c r="G38" t="n">
-        <v>33.90029</v>
+        <v>33.96684</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17.30898</v>
+        <v>16.94874</v>
       </c>
       <c r="D39" t="n">
-        <v>15.86076</v>
+        <v>16.03607</v>
       </c>
       <c r="E39" t="n">
-        <v>16.3146</v>
+        <v>16.34029</v>
       </c>
       <c r="F39" t="n">
-        <v>21.91538</v>
+        <v>22.51662</v>
       </c>
       <c r="G39" t="n">
-        <v>34.60527</v>
+        <v>33.77526</v>
       </c>
     </row>
     <row r="40">
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.77473</v>
+        <v>16.94523</v>
       </c>
       <c r="D40" t="n">
-        <v>16.19328</v>
+        <v>16.16017</v>
       </c>
       <c r="E40" t="n">
-        <v>16.44397</v>
+        <v>16.51642</v>
       </c>
       <c r="F40" t="n">
-        <v>21.75152</v>
+        <v>21.75402</v>
       </c>
       <c r="G40" t="n">
-        <v>34.58986</v>
+        <v>35.16205</v>
       </c>
     </row>
     <row r="41">
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16.85234</v>
+        <v>16.86134</v>
       </c>
       <c r="D42" t="n">
-        <v>16.28871</v>
+        <v>16.20695</v>
       </c>
       <c r="E42" t="n">
-        <v>16.44513</v>
+        <v>16.64673</v>
       </c>
       <c r="F42" t="n">
-        <v>22.1979</v>
+        <v>22.21712</v>
       </c>
       <c r="G42" t="n">
-        <v>34.40853</v>
+        <v>34.20325</v>
       </c>
     </row>
     <row r="43">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.67562</v>
+        <v>16.72575</v>
       </c>
       <c r="D43" t="n">
-        <v>16.18999</v>
+        <v>16.13898</v>
       </c>
       <c r="E43" t="n">
-        <v>16.4338</v>
+        <v>16.69672</v>
       </c>
       <c r="F43" t="n">
-        <v>21.53741</v>
+        <v>21.30619</v>
       </c>
       <c r="G43" t="n">
-        <v>35.0739</v>
+        <v>34.61043</v>
       </c>
     </row>
     <row r="44">
@@ -1451,19 +1451,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16.6845</v>
+        <v>16.79161</v>
       </c>
       <c r="D44" t="n">
-        <v>16.13659</v>
+        <v>15.90412</v>
       </c>
       <c r="E44" t="n">
-        <v>16.76299</v>
+        <v>16.40335</v>
       </c>
       <c r="F44" t="n">
-        <v>21.92079</v>
+        <v>21.64632</v>
       </c>
       <c r="G44" t="n">
-        <v>34.19395</v>
+        <v>34.12822</v>
       </c>
     </row>
     <row r="45">
@@ -1473,19 +1473,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.74955</v>
+        <v>16.70338</v>
       </c>
       <c r="D45" t="n">
-        <v>16.08841</v>
+        <v>16.16754</v>
       </c>
       <c r="E45" t="n">
-        <v>16.47057</v>
+        <v>16.37437</v>
       </c>
       <c r="F45" t="n">
-        <v>21.67427</v>
+        <v>21.67885</v>
       </c>
       <c r="G45" t="n">
-        <v>34.58193</v>
+        <v>34.89684</v>
       </c>
     </row>
     <row r="46">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.57241</v>
+        <v>16.63602</v>
       </c>
       <c r="D46" t="n">
-        <v>16.13355</v>
+        <v>15.99428</v>
       </c>
       <c r="E46" t="n">
-        <v>16.43293</v>
+        <v>16.39744</v>
       </c>
       <c r="F46" t="n">
-        <v>21.9928</v>
+        <v>21.69486</v>
       </c>
       <c r="G46" t="n">
-        <v>34.21921</v>
+        <v>34.00435</v>
       </c>
     </row>
     <row r="47">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.6672</v>
+        <v>16.65237</v>
       </c>
       <c r="D47" t="n">
-        <v>15.90792</v>
+        <v>16.0387</v>
       </c>
       <c r="E47" t="n">
-        <v>16.45037</v>
+        <v>16.05679</v>
       </c>
       <c r="F47" t="n">
-        <v>21.64852</v>
+        <v>21.96564</v>
       </c>
       <c r="G47" t="n">
-        <v>34.80646</v>
+        <v>34.00305</v>
       </c>
     </row>
     <row r="48">
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.64005</v>
+        <v>16.83023</v>
       </c>
       <c r="D48" t="n">
-        <v>16.17856</v>
+        <v>15.98191</v>
       </c>
       <c r="E48" t="n">
-        <v>16.54445</v>
+        <v>16.54999</v>
       </c>
       <c r="F48" t="n">
-        <v>21.98637</v>
+        <v>21.9584</v>
       </c>
       <c r="G48" t="n">
-        <v>34.49942</v>
+        <v>34.04623</v>
       </c>
     </row>
     <row r="49">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.48403</v>
+        <v>16.70023</v>
       </c>
       <c r="D49" t="n">
-        <v>15.90395</v>
+        <v>15.77651</v>
       </c>
       <c r="E49" t="n">
-        <v>16.46728</v>
+        <v>16.67716</v>
       </c>
       <c r="F49" t="n">
-        <v>22.17205</v>
+        <v>22.04795</v>
       </c>
       <c r="G49" t="n">
-        <v>34.67902</v>
+        <v>34.28757</v>
       </c>
     </row>
     <row r="50">
@@ -1583,19 +1583,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16.64248</v>
+        <v>16.56411</v>
       </c>
       <c r="D50" t="n">
-        <v>15.86673</v>
+        <v>16.2173</v>
       </c>
       <c r="E50" t="n">
-        <v>16.26797</v>
+        <v>16.53838</v>
       </c>
       <c r="F50" t="n">
-        <v>21.74045</v>
+        <v>22.05565</v>
       </c>
       <c r="G50" t="n">
-        <v>34.89966</v>
+        <v>35.05627</v>
       </c>
     </row>
     <row r="51">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.6257</v>
+        <v>0.61264</v>
       </c>
       <c r="D52" t="n">
-        <v>1.10968</v>
+        <v>1.12743</v>
       </c>
     </row>
     <row r="53">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.60488</v>
+        <v>0.60234</v>
       </c>
       <c r="D53" t="n">
-        <v>1.1464</v>
+        <v>1.10608</v>
       </c>
     </row>
     <row r="54">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.61275</v>
+        <v>0.62256</v>
       </c>
       <c r="D54" t="n">
-        <v>1.12766</v>
+        <v>1.11399</v>
       </c>
     </row>
     <row r="55">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.61502</v>
       </c>
       <c r="D55" t="n">
-        <v>1.116</v>
+        <v>1.11666</v>
       </c>
     </row>
     <row r="56">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.60164</v>
+        <v>0.61486</v>
       </c>
       <c r="D56" t="n">
-        <v>1.11884</v>
+        <v>1.10761</v>
       </c>
     </row>
     <row r="57">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.60715</v>
+        <v>0.60727</v>
       </c>
       <c r="D57" t="n">
-        <v>1.10567</v>
+        <v>1.10758</v>
       </c>
     </row>
     <row r="58">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.60605</v>
+        <v>0.61705</v>
       </c>
       <c r="D58" t="n">
-        <v>1.11397</v>
+        <v>1.10622</v>
       </c>
     </row>
     <row r="59">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.60003</v>
+        <v>0.61403</v>
       </c>
       <c r="D59" t="n">
-        <v>1.10989</v>
+        <v>1.12086</v>
       </c>
     </row>
     <row r="60">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.61647</v>
+        <v>0.6148400000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>1.1084</v>
+        <v>1.13687</v>
       </c>
     </row>
     <row r="61">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.61833</v>
+        <v>0.60398</v>
       </c>
       <c r="D62" t="n">
-        <v>1.10976</v>
+        <v>1.10269</v>
       </c>
     </row>
     <row r="63">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.61232</v>
+        <v>0.60729</v>
       </c>
       <c r="D63" t="n">
-        <v>1.08171</v>
+        <v>1.12458</v>
       </c>
     </row>
     <row r="64">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.60975</v>
+        <v>0.61881</v>
       </c>
       <c r="D64" t="n">
-        <v>1.12198</v>
+        <v>1.13652</v>
       </c>
     </row>
     <row r="65">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.61212</v>
+        <v>0.60399</v>
       </c>
       <c r="D65" t="n">
-        <v>1.1305</v>
+        <v>1.10802</v>
       </c>
     </row>
     <row r="66">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.6118</v>
+        <v>0.61779</v>
       </c>
       <c r="D66" t="n">
-        <v>1.11074</v>
+        <v>1.13021</v>
       </c>
     </row>
     <row r="67">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.6052</v>
+        <v>0.5952499999999999</v>
       </c>
       <c r="D67" t="n">
-        <v>1.13004</v>
+        <v>1.12966</v>
       </c>
     </row>
     <row r="68">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.6160099999999999</v>
+        <v>0.61289</v>
       </c>
       <c r="D68" t="n">
-        <v>1.12364</v>
+        <v>1.14417</v>
       </c>
     </row>
     <row r="69">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.61211</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>1.14703</v>
+        <v>1.10951</v>
       </c>
     </row>
     <row r="70">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.61527</v>
+        <v>0.61152</v>
       </c>
       <c r="D70" t="n">
-        <v>1.10818</v>
+        <v>1.12173</v>
       </c>
     </row>
   </sheetData>
